--- a/SCRIPTS/APPLICATIONS/logS_MAD.xlsx
+++ b/SCRIPTS/APPLICATIONS/logS_MAD.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6f33fa7f78ea46e2aaca-my.sharepoint.com/personal/william_zamoraramirez_ucr_ac_cr/Documents/Backup/SOLUBILIDAD/SCRIPTS/APPLICATIONS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="8_{F50348C8-B5D8-4C51-85ED-42AA902F785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E12F3B1F-2E3C-467F-934E-8511E9D1AFEF}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{F50348C8-B5D8-4C51-85ED-42AA902F785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AD95C6B-9364-4B98-8E14-5A6455B768CE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{F8B66F25-B9A1-423C-BEED-979EBF1600A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Ref 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -607,7 +608,7 @@
     <col min="2" max="2" width="20.26953125" customWidth="1"/>
     <col min="3" max="3" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.81640625" bestFit="1" customWidth="1"/>
@@ -1228,4 +1229,13 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE615792-FCD3-42EF-9613-8D2EC4B1234A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>